--- a/source-data/Enerium_Лутбоксы.xlsx
+++ b/source-data/Enerium_Лутбоксы.xlsx
@@ -192,7 +192,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">08eb472702bd749a — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">3a70944c50589edc — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1318,17 +1318,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовые боссы</t>
+          <t xml:space="preserve">Призванные враги</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">победа над врагом, призванным предметом крафта: руина, город, эхо босса биома, пробуждённый (§12.3, §17.1, ADR-0023, п. 4)</t>
+          <t xml:space="preserve">победа над врагом, призванным предметом крафта: босс руины, эхо босса биома, босс города, пробуждённый (§12.3, §17.1, ADR-0023, п. 4, ADR-0039)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук крафтового босса</t>
+          <t xml:space="preserve">Сундук призыва</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">

--- a/source-data/Enerium_Лутбоксы.xlsx
+++ b/source-data/Enerium_Лутбоксы.xlsx
@@ -14,12 +14,12 @@
     <sheet name="Пулы" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сундуки'!$A$1:$F$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Линии'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сундуки'!$A$1:$F$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Линии'!$A$1:$F$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Редкости и окна'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Источники'!$A$1:$G$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Источники'!$A$1:$G$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Призванные враги'!$A$1:$H$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Пулы'!$A$1:$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Пулы'!$A$1:$C$14</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -180,7 +180,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
+          <t xml:space="preserve">2026-10-07 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
         </is>
       </c>
     </row>
@@ -192,7 +192,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a70944c50589edc — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">b7a77bef9232971a — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -229,7 +229,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">7 строк.</t>
+          <t xml:space="preserve">23 строки.</t>
         </is>
       </c>
     </row>
@@ -241,7 +241,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 строк.</t>
+          <t xml:space="preserve">24 строки.</t>
         </is>
       </c>
     </row>
@@ -265,7 +265,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 строк.</t>
+          <t xml:space="preserve">27 строк.</t>
         </is>
       </c>
     </row>
@@ -289,7 +289,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 строк.</t>
+          <t xml:space="preserve">13 строк.</t>
         </is>
       </c>
     </row>
@@ -319,8 +319,8 @@
 III — слабые, почти незаметные намёки — слово-отзвук без имени тайны (ADR-0022: намёки на Странника — с цикла III)
 IV — заметнее, но всё ещё намёки: иносказание, без прямых имён и формулировок тайны
 V — намёки очевиднее («начиная с 5 будут намёки»); прямого раскрытия §38 нет
-VI — только для команды: здесь тайны названы прямо
-Ступени слов: D — прямое раскрытие — только цикл VI, для команды; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
+VI — раскрытие: в текстах игрока цикла VI тайны могут быть названы прямо (ADR-0054); в текстах циклов I–V — нет
+Ступени слов: D — прямое раскрытие — только с цикла VI: игрок получает его в игре, раньше — нет; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
 Проверка — node tools/content-gen/tables/check_spoilers.js; все совпадения по циклам — «Реестр имён», лист «Намёки по циклам».</t>
         </is>
       </c>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -404,7 +404,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 / 2 / 3 / 3 / 3 / 3 / 3</t>
+          <t xml:space="preserve">1 / 2 / 3 / 3 / 3 / 3 / 3</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -463,7 +463,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Предмет снаряжения 80 %; Ресурсы 20 %</t>
+          <t xml:space="preserve">Предмет снаряжения 80 %; Ресурсы 20 %; Предмет снаряжения 72 %; Ресурсы 28 %</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Духовный талисман 80 %; Ресурсы 20 %</t>
+          <t xml:space="preserve">Духовный талисман 80 %; Ресурсы 20 %; Духовный талисман 45 %; Ресурсы 55 %; Духовный талисман 36 %; Ресурсы 64 %</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Шарды рабочего 75 %; Ресурсы 25 %</t>
+          <t xml:space="preserve">Шарды рабочего 75 %; Ресурсы 25 %; Шарды рабочего 50 %; Ресурсы 50 %; Шарды рабочего 42 %; Ресурсы 58 %</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -549,22 +549,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">craft</t>
+          <t xml:space="preserve">loot</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Добыча</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Шарды рабочего 57 %; Духовный талисман 40 %; Рунные ключи 3 %</t>
+          <t xml:space="preserve">Базовые ресурсы 25 %; Ключи ремёсел 25 %; Ресурсы мест и находки 25 %; Прах душ 15 %; Предмет снаряжения 5 %; Руна предела IV–V 4 %; Осколки доблести 1 %</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 / 2 / 3 / 3 / 3 / 3 / 3</t>
+          <t xml:space="preserve">2 / 2 / 2 / 2 / 2 / 2 / 2</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -574,50 +574,554 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">craftV</t>
+          <t xml:space="preserve">rv</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t xml:space="preserve">loot_u</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Добыча города</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Базовые ресурсы 25 %; Ключи ремёсел 25 %; Ресурсы мест и находки 25 %; Прах душ 15 %; Предмет снаряжения 5 %; Руна предела IV–V 4 %; Осколки доблести 1 %</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 / 2 / 2 / 2 / 2 / 2 / 2</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото: 1000 / 1500 / 2000 / 2500 / 3000 / 3500 / 4000</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rv</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">loot_a</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Добыча пробуждённого</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Базовые ресурсы 25 %; Ключи ремёсел 25 %; Ресурсы мест и находки 25 %; Прах душ 15 %; Предмет снаряжения 5 %; Руна предела IV–V 4 %; Осколки доблести 1 %</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 / 2 / 2 / 2 / 2 / 2 / 2</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото: 2000 / 3000 / 4000 / 5000 / 6000 / 7000 / 8000</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rv</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vault</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Казна</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото 24 %; Дух 33 %; Прах душ 30 %; Рунные ключи 3 %; Предмет снаряжения 5 %; Руна предела IV–V 4 %; Осколки доблести 1 %</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 / 2 / 2 / 2 / 2 / 2 / 2</t>
+        </is>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rv</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vault_a</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Казна пробуждённого</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото 24 %; Дух 33 %; Прах душ 30 %; Рунные ключи 3 %; Предмет снаряжения 5 %; Руна предела IV–V 4 %; Осколки доблести 1 %</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 / 2 / 2 / 2 / 2 / 2 / 2</t>
+        </is>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rv</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">forge</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Горн</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Руна предела III–V 45 %; Ключи кузнечества 45 %; Руна предела IV–V 8 %; Осколки доблести 2 %</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 / 2 / 2 / 2 / 2 / 2 / 2</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото: 1000 / 1500 / 2000 / 2500 / 3000 / 3500 / 4000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rv</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">forge_u</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Горн города</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Руна предела III–V 45 %; Ключи кузнечества 45 %; Руна предела IV–V 8 %; Осколки доблести 2 %</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 / 2 / 2 / 2 / 2 / 2 / 2</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото: 1000 / 1500 / 2000 / 2500 / 3000 / 3500 / 4000</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rv</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">forge_a</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Горн пробуждённого</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Руна предела III–V 45 %; Ключи кузнечества 45 %; Руна предела IV–V 8 %; Осколки доблести 2 %</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 / 2 / 2 / 2 / 2 / 2 / 2</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото: 2000 / 3000 / 4000 / 5000 / 6000 / 7000 / 8000</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rv</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">runes</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рунный ларь</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Руна предела 25 %; Ключи зачарования 55 %; Осколки доблести 9 %; Руна доблести 1 %; Предмет снаряжения 10 %</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 / 2 / 2 / 2 / 2 / 2 / 2</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото: 1000 / 1500 / 2000 / 2500 / 3000 / 3500 / 4000</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rv</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">runes_u</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рунный ларь города</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Руна предела 25 %; Ключи зачарования 55 %; Осколки доблести 9 %; Руна доблести 1 %; Предмет снаряжения 10 %</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 / 2 / 2 / 2 / 2 / 2 / 2</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото: 1000 / 1500 / 2000 / 2500 / 3000 / 3500 / 4000</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rv</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">runes_a</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рунный ларь пробуждённого</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Руна предела 25 %; Ключи зачарования 55 %; Осколки доблести 9 %; Руна доблести 1 %; Предмет снаряжения 10 %</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 / 2 / 2 / 2 / 2 / 2 / 2</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото: 2000 / 3000 / 4000 / 5000 / 6000 / 7000 / 8000</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rv</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">urn</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Урна имён</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Осколки героя Эхо 25 %; Прах душ 65 %; Предмет снаряжения 5 %; Руна предела IV–V 4 %; Осколки доблести 1 %</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 / 2 / 2 / 2 / 2 / 2 / 2</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото: 1000 / 1500 / 2000 / 2500 / 3000 / 3500 / 4000</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rv</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">urn_u</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Урна имён города</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Осколки героя Эхо 25 %; Прах душ 65 %; Предмет снаряжения 5 %; Руна предела IV–V 4 %; Осколки доблести 1 %</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 / 2 / 2 / 2 / 2 / 2 / 2</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото: 1000 / 1500 / 2000 / 2500 / 3000 / 3500 / 4000</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rv</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">urn_a</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Урна имён пробуждённого</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Осколки героя Эхо 25 %; Прах душ 65 %; Предмет снаряжения 5 %; Руна предела IV–V 4 %; Осколки доблести 1 %</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 / 2 / 2 / 2 / 2 / 2 / 2</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото: 2000 / 3000 / 4000 / 5000 / 6000 / 7000 / 8000</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rv</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craft</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сундук призыва</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Шарды рабочего 20 %; Духовный талисман 20 %; Ресурсы биомов 37 %; Прах душ 10 %; Рунные ключи 3 %; Предмет снаряжения 5 %; Руна предела IV–V 4 %; Осколки доблести 1 %</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 / 2 / 2 / 2 / 2 / 2 / 2</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото: 1000 / 1500 / 2000 / 2500 / 3000 / 3500 / 4000</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rv</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craft_a</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сундук призыва пробуждённого</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Шарды рабочего 20 %; Духовный талисман 20 %; Ресурсы биомов 37 %; Прах душ 10 %; Рунные ключи 3 %; Предмет снаряжения 5 %; Руна предела IV–V 4 %; Осколки доблести 1 %</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 / 2 / 2 / 2 / 2 / 2 / 2</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото: 2000 / 3000 / 4000 / 5000 / 6000 / 7000 / 8000</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rv</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t xml:space="preserve">wander</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t xml:space="preserve">Сундук странника</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ресурсы 55 %; Прах душ 45 %; Рунные ключи 3 %</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t xml:space="preserve">1 / 1 / 2 / 2 / 2 / 3 / 3</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Золото: 1000 / 1500 / 2000 / 2500 / 3000 / 3500 / 4000; Дух: 2000 / 3000 / 4000 / 5000 / 6000 / 7000 / 8000</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">dust</t>
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artel</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сундук артели</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ресурсы биомов 70 %; Прах душ 30 %</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 / 2 / 3 / 3 / 3 / 3 / 3</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото: 1000 / 1500 / 2000 / 2500 / 3000 / 3500 / 4000</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dust</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F8"/>
+  <autoFilter ref="A1:F24"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -663,79 +1167,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shards</t>
+          <t xml:space="preserve">target</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Осколки героя недели</t>
+          <t xml:space="preserve">Осколки героя-цели недели</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shards</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6; 12; 16; 24; 36; 54; 80</t>
-        </is>
-      </c>
+          <t xml:space="preserve">target</t>
+        </is>
+      </c>
+      <c r="D2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">workers</t>
+          <t xml:space="preserve">shards</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Шарды рабочего</t>
+          <t xml:space="preserve">Осколки героя недели</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">workers</t>
+          <t xml:space="preserve">shards</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3; 3; 3; 3; 3; 3; 3</t>
+          <t xml:space="preserve">25; 50; 100; 200; 400; 800; 1600</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">tal</t>
+          <t xml:space="preserve">workers</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Духовный талисман</t>
+          <t xml:space="preserve">Шарды рабочего</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">tal</t>
-        </is>
-      </c>
-      <c r="D4" s="3"/>
+          <t xml:space="preserve">workers</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3; 3; 3; 3; 3; 3; 3</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">equip</t>
+          <t xml:space="preserve">tal</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Предмет снаряжения</t>
+          <t xml:space="preserve">Духовный талисман</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">equip</t>
+          <t xml:space="preserve">tal</t>
         </is>
       </c>
       <c r="D5" s="3"/>
@@ -743,34 +1247,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">keys</t>
+          <t xml:space="preserve">equip</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Рунные ключи</t>
+          <t xml:space="preserve">Предмет снаряжения</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">cur</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2; 3; 4; 6; 8; 10; 12</t>
-        </is>
-      </c>
+          <t xml:space="preserve">equip</t>
+        </is>
+      </c>
+      <c r="D6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">dust</t>
+          <t xml:space="preserve">keys</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Прах душ</t>
+          <t xml:space="preserve">Рунные ключи</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -780,71 +1280,419 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5; 10; 20; 40; 80; 160; 320</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">II</t>
+          <t xml:space="preserve">2; 3; 4; 6; 8; 10; 12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">res</t>
+          <t xml:space="preserve">dust</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ресурсы</t>
+          <t xml:space="preserve">Прах душ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">res</t>
+          <t xml:space="preserve">cur</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">basic,3; basic,6; key,1; key,2; key,3; unique,1; unique,2</t>
+          <t xml:space="preserve">5; 10; 20; 40; 80; 160; 320</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">II</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t xml:space="preserve">res</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ресурсы</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">res</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">basic,3; basic,6; key,1; key,2; key,3; unique,1; unique,2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">field</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ресурсы биомов</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">res</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">basic,3; basic,6; key,1; key,2; key,3; key,4; key,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t xml:space="preserve">many</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t xml:space="preserve">Многоликий</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">item</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">; ; ; many,1; ; ; </t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t xml:space="preserve">II</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lbasic</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Базовые ресурсы</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">res</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">basic,8; basic,12; basic,16; basic,24; basic,32; basic,48; basic,64</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lkey</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ключи ремёсел</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">res</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">key,2; key,3; key,4; key,6; key,8; key,12; key,16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lplace</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ресурсы мест и находки</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">res</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craftres,2; craftres,3; craftres,4; craftres,6; craftres,8; find,1; find,2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gold</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cur</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2000; 4000; 8000; 16000; 32000; 64000; 128000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spirit</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дух</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cur</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4000; 8000; 16000; 32000; 64000; 128000; 256000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smithkey</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ключи кузнечества</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">res</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">key_smith,2; key_smith,3; key_smith,4; key_smith,6; key_smith,8; key_smith,12; key_smith,16</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rune</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Руна предела</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">runes</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1; 1; 1; 1; 1; 1; 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rune35</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Руна предела III–V</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">runes</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1; 1; 1; 1; 1; 1; 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">srune</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Руна предела IV–V</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">runes</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1; 1; 1; 1; 1; 1; 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vshard</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Осколки доблести</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">res</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vshard,1; vshard,1; vshard,1; vshard,1; vshard,2; vshard,2; vshard,3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enchkey</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ключи зачарования</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">res</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">key_ench,2; key_ench,3; key_ench,4; key_ench,6; key_ench,8; key_ench,12; key_ench,16</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valor</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Руна доблести</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">res</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">; ; ; ; ; valor,1; valor,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rshards</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Осколки героя возрождения душ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rshards</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5; 5; 5; 5; 10; 15; 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etarget</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Осколки героя Эхо</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target</t>
+        </is>
+      </c>
+      <c r="D25" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F9"/>
+  <autoFilter ref="A1:F25"/>
 </worksheet>
 </file>
 
@@ -1069,7 +1917,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1264,7 +2112,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">место клана и личные очки (§25.3): планок нет</t>
+          <t xml:space="preserve">личные очки недели и круги клана — ступени; места клана и личные (§25.3)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1281,22 +2129,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">event</t>
+          <t xml:space="preserve">ritual</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Событие</t>
+          <t xml:space="preserve">Ритуалы</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук рабочих</t>
+          <t xml:space="preserve">Сундук артели</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">очки События за неделю (§27)</t>
+          <t xml:space="preserve">загрузка своих мест ритуалов за неделю, % (§19)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1313,155 +2161,592 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">craft</t>
+          <t xml:space="preserve">event</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призванные враги</t>
+          <t xml:space="preserve">Событие</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Сундук рабочих</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">победа над врагом, призванным предметом крафта: босс руины, эхо босса биома, босс города, пробуждённый (§12.3, §17.1, ADR-0023, п. 4, ADR-0039)</t>
+          <t xml:space="preserve">очки События за неделю (§27)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
+          <t xml:space="preserve">II</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">mask</t>
+          <t xml:space="preserve">loot</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лик недели</t>
+          <t xml:space="preserve">Призванные враги · Добыча</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук осколков</t>
+          <t xml:space="preserve">Добыча</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">победа над Ликом недели — врагом из «Маски недели» (§17.1, ADR-0025)</t>
+          <t xml:space="preserve">победа над врагом, призванным предметом крафта (§12.3, §17.1, ADR-0023, п. 4, ADR-0039): сундук своей темы — по ремеслу цепочки рецептов врага (ADR-0047)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">II</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">first</t>
+          <t xml:space="preserve">loot_u</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Первая победа над боссом биома</t>
+          <t xml:space="preserve">Призванные враги · Добыча города</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук странника</t>
+          <t xml:space="preserve">Добыча города</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">первое убийство босса биома — раз на аккаунт</t>
+          <t xml:space="preserve">победа над врагом, призванным предметом крафта (§12.3, §17.1, ADR-0023, п. 4, ADR-0039): сундук своей темы — по ремеслу цепочки рецептов врага (ADR-0047)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
+          <t xml:space="preserve">VI</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">feats</t>
+          <t xml:space="preserve">loot_a</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Достижения</t>
+          <t xml:space="preserve">Призванные враги · Добыча пробуждённого</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук странника</t>
+          <t xml:space="preserve">Добыча пробуждённого</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">получение достижения (§29) — цикл игрока в этот момент</t>
+          <t xml:space="preserve">победа над врагом, призванным предметом крафта (§12.3, §17.1, ADR-0023, п. 4, ADR-0039): сундук своей темы — по ремеслу цепочки рецептов врага (ADR-0047)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
+          <t xml:space="preserve">III</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t xml:space="preserve">vault</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги · Казна</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Казна</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">победа над врагом, призванным предметом крафта (§12.3, §17.1, ADR-0023, п. 4, ADR-0039): сундук своей темы — по ремеслу цепочки рецептов врага (ADR-0047)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vault_a</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги · Казна пробуждённого</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Казна пробуждённого</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">победа над врагом, призванным предметом крафта (§12.3, §17.1, ADR-0023, п. 4, ADR-0039): сундук своей темы — по ремеслу цепочки рецептов врага (ADR-0047)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">III</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">forge</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги · Горн</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Горн</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">победа над врагом, призванным предметом крафта (§12.3, §17.1, ADR-0023, п. 4, ADR-0039): сундук своей темы — по ремеслу цепочки рецептов врага (ADR-0047)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">II</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">forge_u</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги · Горн города</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Горн города</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">победа над врагом, призванным предметом крафта (§12.3, §17.1, ADR-0023, п. 4, ADR-0039): сундук своей темы — по ремеслу цепочки рецептов врага (ADR-0047)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">forge_a</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги · Горн пробуждённого</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Горн пробуждённого</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">победа над врагом, призванным предметом крафта (§12.3, §17.1, ADR-0023, п. 4, ADR-0039): сундук своей темы — по ремеслу цепочки рецептов врага (ADR-0047)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">III</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">runes</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги · Рунный ларь</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рунный ларь</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">победа над врагом, призванным предметом крафта (§12.3, §17.1, ADR-0023, п. 4, ADR-0039): сундук своей темы — по ремеслу цепочки рецептов врага (ADR-0047)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">runes_u</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги · Рунный ларь города</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рунный ларь города</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">победа над врагом, призванным предметом крафта (§12.3, §17.1, ADR-0023, п. 4, ADR-0039): сундук своей темы — по ремеслу цепочки рецептов врага (ADR-0047)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">runes_a</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги · Рунный ларь пробуждённого</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рунный ларь пробуждённого</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">победа над врагом, призванным предметом крафта (§12.3, §17.1, ADR-0023, п. 4, ADR-0039): сундук своей темы — по ремеслу цепочки рецептов врага (ADR-0047)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">III</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">urn</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги · Урна имён</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Урна имён</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">победа над врагом, призванным предметом крафта (§12.3, §17.1, ADR-0023, п. 4, ADR-0039): сундук своей темы — по ремеслу цепочки рецептов врага (ADR-0047)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">III</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">urn_u</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги · Урна имён города</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Урна имён города</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">победа над врагом, призванным предметом крафта (§12.3, §17.1, ADR-0023, п. 4, ADR-0039): сундук своей темы — по ремеслу цепочки рецептов врага (ADR-0047)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">urn_a</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги · Урна имён пробуждённого</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Урна имён пробуждённого</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">победа над врагом, призванным предметом крафта (§12.3, §17.1, ADR-0023, п. 4, ADR-0039): сундук своей темы — по ремеслу цепочки рецептов врага (ADR-0047)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craft</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги · Сундук призыва</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сундук призыва</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">победа над врагом, призванным предметом крафта (§12.3, §17.1, ADR-0023, п. 4, ADR-0039): сундук своей темы — по ремеслу цепочки рецептов врага (ADR-0047)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craft_a</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Призванные враги · Сундук призыва пробуждённого</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сундук призыва пробуждённого</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">победа над врагом, призванным предметом крафта (§12.3, §17.1, ADR-0023, п. 4, ADR-0039): сундук своей темы — по ремеслу цепочки рецептов врага (ADR-0047)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mask</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лик недели</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сундук осколков</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">победа над Ликом недели — врагом из «Маски недели» (§17.1, ADR-0025)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">II</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">first</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Первая победа над боссом биома</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сундук странника</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">первое убийство босса биома — раз на аккаунт</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feats</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Достижения</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сундук странника</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">получение достижения (§29) — цикл игрока в этот момент</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t xml:space="preserve">calendar</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t xml:space="preserve">Календарь</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t xml:space="preserve">Сундук странника</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">лист даров «Дар дня»: 30 отметок за вход в игру (§29); сундуки — на шальных отметках и вехах 7, 14, 20, 30</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t xml:space="preserve">I</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">да</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:G28"/>
 </worksheet>
 </file>
 
@@ -1545,7 +2830,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Добыча</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1585,7 +2870,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Казна</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1625,7 +2910,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Горн города</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1665,7 +2950,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Рунный ларь</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1705,7 +2990,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Казна</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1745,7 +3030,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Добыча</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1785,7 +3070,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Горн города</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1825,7 +3110,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Горн</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1865,7 +3150,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Урна имён</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1905,7 +3190,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Казна</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1945,7 +3230,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Горн</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1985,7 +3270,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Горн города</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2025,7 +3310,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Урна имён</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2065,7 +3350,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Добыча</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2105,7 +3390,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Казна</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2145,7 +3430,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Казна</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2185,7 +3470,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Урна имён города</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2265,7 +3550,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Рунный ларь</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2305,7 +3590,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Добыча</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2345,7 +3630,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Урна имён</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2385,7 +3670,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Добыча</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2425,7 +3710,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Рунный ларь города</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2465,7 +3750,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Рунный ларь</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2505,7 +3790,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Казна</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2545,7 +3830,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Рунный ларь</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2585,7 +3870,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Добыча города</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2625,7 +3910,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Рунный ларь</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2665,7 +3950,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Добыча</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2705,7 +3990,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Казна</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2745,7 +4030,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Горн</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2785,7 +4070,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Горн</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2825,7 +4110,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Горн</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2865,7 +4150,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Горн</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2905,7 +4190,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Горн</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2985,7 +4270,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Казна</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3025,7 +4310,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Урна имён</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3065,7 +4350,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Добыча</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3105,7 +4390,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Добыча пробуждённого</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3145,7 +4430,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Казна пробуждённого</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3185,7 +4470,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Горн пробуждённого</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3225,7 +4510,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Рунный ларь пробуждённого</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3265,7 +4550,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Казна пробуждённого</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3305,7 +4590,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Добыча пробуждённого</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3345,7 +4630,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Горн пробуждённого</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3385,7 +4670,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Горн пробуждённого</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3425,7 +4710,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Урна имён пробуждённого</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3465,7 +4750,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Казна пробуждённого</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3505,7 +4790,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Горн пробуждённого</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3545,7 +4830,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Горн пробуждённого</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3585,7 +4870,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Урна имён пробуждённого</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3625,7 +4910,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Добыча пробуждённого</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3665,7 +4950,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Казна пробуждённого</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3705,7 +4990,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Казна пробуждённого</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3745,7 +5030,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Урна имён пробуждённого</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3785,7 +5070,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Сундук призыва пробуждённого</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3825,7 +5110,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Рунный ларь пробуждённого</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3865,7 +5150,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Добыча пробуждённого</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3905,7 +5190,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Урна имён пробуждённого</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3945,7 +5230,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Добыча пробуждённого</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3985,7 +5270,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Рунный ларь пробуждённого</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4025,7 +5310,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Рунный ларь пробуждённого</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4065,7 +5350,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Казна пробуждённого</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4105,7 +5390,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Рунный ларь пробуждённого</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4145,7 +5430,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сундук призыва</t>
+          <t xml:space="preserve">Добыча пробуждённого</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4204,7 +5489,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4277,34 +5562,154 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">heroes</t>
+          <t xml:space="preserve">craftres</t>
         </is>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Люди: 5; Дворфы: 5; Эльфы: 5; Звери: 5; Саганы: 5; Аппараты: 5; Искажённые: 5; Нежить: 5; Забытые: 5</t>
+          <t xml:space="preserve">1: 30; 2: 39; 3: 48; 4: 48; 5: 57; 6: 39</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t xml:space="preserve">find</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1: 6; 2: 8; 3: 10; 4: 10; 5: 12; 6: 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rune</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1: 5; 2: 5; 3: 5; 4: 5; 5: 5; 6: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vshard</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1: 1; 2: 1; 3: 1; 4: 1; 5: 1; 6: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valor</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1: 1; 2: 1; 3: 1; 4: 1; 5: 1; 6: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roulette</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1: 0; 2: 10; 3: 8; 4: 8; 5: 6; 6: 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heroes</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Люди: 5; Дворфы: 5; Эльфы: 5; Звери: 5; Саганы: 5; Аппараты: 5; Искажённые: 5; Нежить: 5; Забытые: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t xml:space="preserve">tal</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="B12">
         <v>7</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1: 77; 2: 42; 3: 42; 4: 41; 5: 55; 6: 54; 7: 48</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">key_smith</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1: 2; 2: 2; 3: 2; 4: 2; 5: 2; 6: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">key_ench</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1: 2; 2: 2; 3: 2; 4: 2; 5: 2; 6: 2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C6"/>
+  <autoFilter ref="A1:C14"/>
 </worksheet>
 </file>